--- a/Provisorios/ProvisorioFile.xlsx
+++ b/Provisorios/ProvisorioFile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesley.oliveira\WS_OLIVEIRA\SCRIPTS\Provisorios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734D9A7F-5FCE-454C-BFD1-6FDF5AD0E536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAB7620-C3B7-4589-BCD2-BD83D3D15278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" tabRatio="917" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="917" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="transferencia" sheetId="1" r:id="rId1"/>
@@ -455,164 +455,73 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>428002</v>
-      </c>
-      <c r="B2">
-        <v>1102105</v>
-      </c>
+      <c r="A2" s="1"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>428009</v>
-      </c>
-      <c r="B3">
-        <v>1102106</v>
-      </c>
+      <c r="A3" s="1"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>429873</v>
-      </c>
-      <c r="B4">
-        <v>1102107</v>
-      </c>
+      <c r="A4" s="1"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>454768</v>
-      </c>
-      <c r="B5">
-        <v>1102108</v>
-      </c>
+      <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>443816</v>
-      </c>
-      <c r="B6">
-        <v>1102109</v>
-      </c>
+      <c r="A6" s="1"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>443817</v>
-      </c>
-      <c r="B7">
-        <v>1102110</v>
-      </c>
+      <c r="A7" s="1"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>457299</v>
-      </c>
-      <c r="B8">
-        <v>1102111</v>
-      </c>
+      <c r="A8" s="1"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>444527</v>
-      </c>
-      <c r="B9">
-        <v>1102112</v>
-      </c>
+      <c r="A9" s="1"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>455926</v>
-      </c>
-      <c r="B10">
-        <v>1102114</v>
-      </c>
+      <c r="A10" s="1"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>448766</v>
-      </c>
-      <c r="B11">
-        <v>1102115</v>
-      </c>
+      <c r="A11" s="1"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>455918</v>
-      </c>
-      <c r="B12">
-        <v>1102116</v>
-      </c>
+      <c r="A12" s="1"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>457298</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1102117</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="2"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>443818</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1102118</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="2"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>467688</v>
-      </c>
-      <c r="B15" s="2">
-        <v>1102119</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>455923</v>
-      </c>
-      <c r="B16" s="2">
-        <v>1102120</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="2"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>448774</v>
-      </c>
-      <c r="B17" s="2">
-        <v>1102121</v>
-      </c>
+      <c r="A17" s="1"/>
+      <c r="B17" s="2"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>455919</v>
-      </c>
-      <c r="B18" s="2">
-        <v>1102123</v>
-      </c>
+      <c r="A18" s="1"/>
+      <c r="B18" s="2"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>467586</v>
-      </c>
-      <c r="B19" s="2">
-        <v>1102124</v>
-      </c>
+      <c r="A19" s="1"/>
+      <c r="B19" s="2"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>470489</v>
-      </c>
-      <c r="B20" s="2">
-        <v>1102125</v>
-      </c>
+      <c r="A20" s="1"/>
+      <c r="B20" s="2"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>461784</v>
-      </c>
-      <c r="B21" s="2">
-        <v>1102126</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
